--- a/wildlife/reports/United-Kingdom/trend/Abingdon/Flora/Common-Mallow.xlsx
+++ b/wildlife/reports/United-Kingdom/trend/Abingdon/Flora/Common-Mallow.xlsx
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/wildlife/reports/United-Kingdom/trend/Abingdon/Flora/Common-Mallow.xlsx
+++ b/wildlife/reports/United-Kingdom/trend/Abingdon/Flora/Common-Mallow.xlsx
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/wildlife/reports/United-Kingdom/trend/Abingdon/Flora/Common-Mallow.xlsx
+++ b/wildlife/reports/United-Kingdom/trend/Abingdon/Flora/Common-Mallow.xlsx
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/wildlife/reports/United-Kingdom/trend/Abingdon/Flora/Common-Mallow.xlsx
+++ b/wildlife/reports/United-Kingdom/trend/Abingdon/Flora/Common-Mallow.xlsx
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
